--- a/odk/source/crop_sown_registry_prep.xlsx
+++ b/odk/source/crop_sown_registry_prep.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -746,6 +746,11 @@
           <t>repeat_count</t>
         </is>
       </c>
+      <c r="O1" s="39" t="inlineStr">
+        <is>
+          <t>required_message</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customFormat="1" customHeight="1" s="43">
       <c r="A2" s="43" t="inlineStr">
@@ -811,6 +816,11 @@
       <c r="K3" s="46" t="n"/>
       <c r="L3" s="46" t="n"/>
       <c r="M3" s="46" t="n"/>
+      <c r="O3" s="39" t="inlineStr">
+        <is>
+          <t>Enter the Fayda ID (FAN).</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A4" s="46" t="inlineStr">
@@ -877,6 +887,11 @@
       <c r="K5" s="46" t="n"/>
       <c r="L5" s="46" t="n"/>
       <c r="M5" s="46" t="n"/>
+      <c r="O5" s="39" t="inlineStr">
+        <is>
+          <t>Select the production season.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customFormat="1" customHeight="1" s="49">
       <c r="A6" s="50" t="inlineStr">
@@ -981,6 +996,11 @@
       <c r="K9" s="46" t="n"/>
       <c r="L9" s="46" t="n"/>
       <c r="M9" s="46" t="n"/>
+      <c r="O9" s="39" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A10" s="46" t="inlineStr">
@@ -1058,6 +1078,11 @@
         </is>
       </c>
       <c r="L11" s="46" t="n"/>
+      <c r="O11" s="39" t="inlineStr">
+        <is>
+          <t>Select the season.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A12" s="46" t="inlineStr">
@@ -1072,7 +1097,7 @@
       </c>
       <c r="C12" s="46" t="inlineStr">
         <is>
-          <t>Start GC</t>
+          <t>Start Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D12" s="46" t="n"/>
@@ -1098,7 +1123,7 @@
       </c>
       <c r="C13" s="46" t="inlineStr">
         <is>
-          <t>End GC</t>
+          <t>End Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D13" s="46" t="n"/>
@@ -1283,7 +1308,7 @@
       </c>
       <c r="C19" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crop </t>
+          <t>Crop</t>
         </is>
       </c>
       <c r="D19" s="46" t="n"/>
@@ -1304,6 +1329,11 @@
       </c>
       <c r="L19" s="46" t="n"/>
       <c r="M19" s="44" t="n"/>
+      <c r="O19" s="39" t="inlineStr">
+        <is>
+          <t>Select the crop.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A20" s="46" t="inlineStr">
@@ -1484,7 +1514,7 @@
       </c>
       <c r="C26" s="46" t="inlineStr">
         <is>
-          <t>Actual Cultivated Date (GC)</t>
+          <t>Actual Cultivated Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D26" s="46" t="n"/>
@@ -1496,7 +1526,7 @@
       </c>
       <c r="G26" s="46" t="inlineStr">
         <is>
-          <t>Actual Cultivated Date (GC) must be between Start GC and End GC.</t>
+          <t>Actual Cultivated Date (GC) must be between Start Date and End Date.</t>
         </is>
       </c>
       <c r="H26" s="46" t="n"/>
@@ -1590,6 +1620,11 @@
       <c r="J29" s="46" t="n"/>
       <c r="K29" s="46" t="n"/>
       <c r="L29" s="46" t="n"/>
+      <c r="O29" s="39" t="inlineStr">
+        <is>
+          <t>Enter the actual crop area (ha).</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A30" s="46" t="inlineStr">
@@ -1604,7 +1639,7 @@
       </c>
       <c r="C30" s="46" t="inlineStr">
         <is>
-          <t>Actual Yield (quintal)</t>
+          <t>Actual Yield (quintals)</t>
         </is>
       </c>
       <c r="D30" s="46" t="n"/>
@@ -1668,7 +1703,7 @@
       </c>
       <c r="C32" s="46" t="inlineStr">
         <is>
-          <t>Land Prep Methods</t>
+          <t>Land Preparation Methods</t>
         </is>
       </c>
       <c r="D32" s="46" t="n"/>
@@ -1910,7 +1945,7 @@
       </c>
       <c r="C41" s="46" t="inlineStr">
         <is>
-          <t>Water Resource</t>
+          <t>Water Source</t>
         </is>
       </c>
       <c r="D41" s="46" t="n"/>
@@ -1930,6 +1965,11 @@
         </is>
       </c>
       <c r="L41" s="46" t="n"/>
+      <c r="O41" s="39" t="inlineStr">
+        <is>
+          <t>Select the water source.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A42" s="46" t="inlineStr">
@@ -1944,7 +1984,7 @@
       </c>
       <c r="C42" s="46" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Irrigation Method</t>
         </is>
       </c>
       <c r="D42" s="46" t="n"/>
@@ -1970,7 +2010,7 @@
       </c>
       <c r="C43" s="46" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Irrigation Frequency</t>
         </is>
       </c>
       <c r="D43" s="46" t="n"/>
@@ -2010,7 +2050,7 @@
       </c>
       <c r="C45" s="46" t="inlineStr">
         <is>
-          <t>DA Name</t>
+          <t>Development Agent Name</t>
         </is>
       </c>
       <c r="D45" s="46" t="n"/>
@@ -2022,7 +2062,7 @@
       </c>
       <c r="G45" s="46" t="inlineStr">
         <is>
-          <t>DA Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H45" s="46" t="n"/>
@@ -2044,12 +2084,12 @@
       </c>
       <c r="C46" s="46" t="inlineStr">
         <is>
-          <t>DA Mobile Number</t>
+          <t>Development Agent Mobile Number</t>
         </is>
       </c>
       <c r="D46" s="44" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E46" s="46" t="n"/>
@@ -2060,7 +2100,7 @@
       </c>
       <c r="G46" s="44" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H46" s="46" t="n"/>
@@ -2094,7 +2134,7 @@
       </c>
       <c r="G47" s="46" t="inlineStr">
         <is>
-          <t>Supervisor Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H47" s="46" t="n"/>
@@ -2121,7 +2161,7 @@
       </c>
       <c r="D48" s="44" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E48" s="46" t="n"/>
@@ -2132,7 +2172,7 @@
       </c>
       <c r="G48" s="44" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H48" s="46" t="n"/>
@@ -2220,6 +2260,11 @@
       <c r="L51" s="46" t="n"/>
       <c r="M51" s="46" t="n"/>
       <c r="N51" s="39" t="n"/>
+      <c r="O51" s="39" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A52" s="46" t="inlineStr">
@@ -2234,7 +2279,7 @@
       </c>
       <c r="C52" s="56" t="inlineStr">
         <is>
-          <t>FPC Name</t>
+          <t>Farmer Production Cluster (FPC) Name</t>
         </is>
       </c>
       <c r="D52" s="46" t="n"/>
@@ -2294,7 +2339,7 @@
       </c>
       <c r="C54" s="46" t="inlineStr">
         <is>
-          <t>Start GC</t>
+          <t>Start Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D54" s="46" t="n"/>
@@ -2320,7 +2365,7 @@
       </c>
       <c r="C55" s="46" t="inlineStr">
         <is>
-          <t>End GC</t>
+          <t>End Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D55" s="46" t="n"/>
@@ -2744,7 +2789,11 @@
           <t>Total Cultivated Area (Timad)</t>
         </is>
       </c>
-      <c r="D68" s="52" t="n"/>
+      <c r="D68" s="52" t="inlineStr">
+        <is>
+          <t>One Timad is 0.25 hectare.</t>
+        </is>
+      </c>
       <c r="E68" s="52" t="n"/>
       <c r="F68" s="52" t="inlineStr">
         <is>
@@ -2864,7 +2913,7 @@
       </c>
       <c r="C71" s="46" t="inlineStr">
         <is>
-          <t>Actual Plan (ha)</t>
+          <t>Actual Planned Area (ha)</t>
         </is>
       </c>
       <c r="D71" s="52" t="n"/>
@@ -2876,7 +2925,7 @@
       </c>
       <c r="G71" s="44" t="inlineStr">
         <is>
-          <t>Plan (ha) must be 0 or greater and cannot be greater than Total Cultivated Area (ha).</t>
+          <t>Planned Area (ha) must be 0 or greater and cannot be greater than Total Cultivated Area (ha).</t>
         </is>
       </c>
       <c r="H71" s="52" t="n"/>
@@ -2909,7 +2958,7 @@
       </c>
       <c r="C72" s="46" t="inlineStr">
         <is>
-          <t>Actual Collected Land (Quintal)</t>
+          <t>Actual Collected Land (quintals)</t>
         </is>
       </c>
       <c r="D72" s="52" t="n"/>
@@ -2921,7 +2970,7 @@
       </c>
       <c r="G72" s="44" t="inlineStr">
         <is>
-          <t>Actual Collected Land (Quintal) cannot be negative.</t>
+          <t>Actual Collected Land (quintals) cannot be negative.</t>
         </is>
       </c>
       <c r="H72" s="52" t="n"/>
@@ -2954,7 +3003,7 @@
       </c>
       <c r="C73" s="46" t="inlineStr">
         <is>
-          <t>Actual Collected Quintal</t>
+          <t>Actual Quantity Collected (quintals)</t>
         </is>
       </c>
       <c r="D73" s="52" t="n"/>
@@ -2966,7 +3015,7 @@
       </c>
       <c r="G73" s="44" t="inlineStr">
         <is>
-          <t>Actual Collected Quintal cannot be negative.</t>
+          <t>Actual Quantity Collected cannot be negative.</t>
         </is>
       </c>
       <c r="H73" s="52" t="n"/>
@@ -2999,7 +3048,7 @@
       </c>
       <c r="C74" s="46" t="inlineStr">
         <is>
-          <t>Actual Collected by Combiner (ha)</t>
+          <t>Actual Area Collected by Combine Harvester (ha)</t>
         </is>
       </c>
       <c r="D74" s="52" t="n"/>
@@ -3011,7 +3060,7 @@
       </c>
       <c r="G74" s="44" t="inlineStr">
         <is>
-          <t>Actual Collected by Combiner (ha) must be 0 or greater and cannot exceed Actual Plan (ha).</t>
+          <t>Actual Area Collected by Combine Harvester (ha) must be 0 or greater and cannot exceed Actual Planned Area (ha).</t>
         </is>
       </c>
       <c r="H74" s="52" t="n"/>
@@ -3059,7 +3108,7 @@
       </c>
       <c r="C76" s="46" t="inlineStr">
         <is>
-          <t>Water Resource</t>
+          <t>Water Source</t>
         </is>
       </c>
       <c r="D76" s="46" t="n"/>
@@ -3079,6 +3128,11 @@
         </is>
       </c>
       <c r="L76" s="46" t="n"/>
+      <c r="O76" s="39" t="inlineStr">
+        <is>
+          <t>Select the water source.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A77" s="46" t="inlineStr">
@@ -3093,7 +3147,7 @@
       </c>
       <c r="C77" s="46" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Irrigation Method</t>
         </is>
       </c>
       <c r="D77" s="46" t="n"/>
@@ -3119,7 +3173,7 @@
       </c>
       <c r="C78" s="46" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Irrigation Frequency</t>
         </is>
       </c>
       <c r="D78" s="46" t="n"/>
@@ -3186,7 +3240,7 @@
       </c>
       <c r="C81" s="46" t="inlineStr">
         <is>
-          <t>DA Name</t>
+          <t>Development Agent Name</t>
         </is>
       </c>
       <c r="D81" s="46" t="n"/>
@@ -3198,7 +3252,7 @@
       </c>
       <c r="G81" s="46" t="inlineStr">
         <is>
-          <t>DA Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H81" s="46" t="n"/>
@@ -3220,12 +3274,12 @@
       </c>
       <c r="C82" s="46" t="inlineStr">
         <is>
-          <t>DA Mobile Number</t>
+          <t>Development Agent Mobile Number</t>
         </is>
       </c>
       <c r="D82" s="44" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E82" s="46" t="n"/>
@@ -3236,7 +3290,7 @@
       </c>
       <c r="G82" s="44" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H82" s="46" t="n"/>
@@ -3270,7 +3324,7 @@
       </c>
       <c r="G83" s="46" t="inlineStr">
         <is>
-          <t>Supervisor Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H83" s="46" t="n"/>
@@ -3297,7 +3351,7 @@
       </c>
       <c r="D84" s="44" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E84" s="46" t="n"/>
@@ -3308,7 +3362,7 @@
       </c>
       <c r="G84" s="44" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H84" s="46" t="n"/>
@@ -4167,7 +4221,7 @@
       </c>
       <c r="C14" s="44" t="inlineStr">
         <is>
-          <t>Farmer-to-Farmer Exchange /Saved Seed</t>
+          <t>Farmer-to-Farmer Exchange / Saved Seed</t>
         </is>
       </c>
       <c r="D14" s="44" t="n"/>
@@ -4870,7 +4924,7 @@
       </c>
       <c r="C53" s="47" t="inlineStr">
         <is>
-          <t>Bi-weekly</t>
+          <t>Every two weeks</t>
         </is>
       </c>
       <c r="D53" s="54" t="n"/>
@@ -5291,7 +5345,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>Nps</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="D76" s="54" t="n"/>
@@ -5312,7 +5366,7 @@
       </c>
       <c r="C77" s="75" t="inlineStr">
         <is>
-          <t>Npsb</t>
+          <t>NPSB</t>
         </is>
       </c>
       <c r="D77" s="54" t="n"/>
@@ -5333,7 +5387,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>Dap</t>
+          <t>DAP</t>
         </is>
       </c>
       <c r="D78" s="54" t="n"/>
@@ -10924,7 +10978,7 @@
       </c>
       <c r="C344" s="47" t="inlineStr">
         <is>
-          <t>Thrashing Machine</t>
+          <t>Threshing Machine</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10995,7 @@
       </c>
       <c r="C345" s="47" t="inlineStr">
         <is>
-          <t>Family Labor</t>
+          <t>Family Labour</t>
         </is>
       </c>
     </row>
@@ -10975,7 +11029,7 @@
       </c>
       <c r="C347" s="47" t="inlineStr">
         <is>
-          <t>Hired Labor</t>
+          <t>Hired Labour</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11101,7 @@
       </c>
       <c r="C352" s="47" t="inlineStr">
         <is>
-          <t>Tractor Disc/Moldboard Ploughing</t>
+          <t>Tractor Disc / Moldboard Ploughing</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11169,7 @@
       </c>
       <c r="C356" s="47" t="inlineStr">
         <is>
-          <t>Manual leveling</t>
+          <t>Manual Levelling</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12074,7 @@
     <row r="2" ht="15" customHeight="1" s="45">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>CSR – 2. Cultivation &amp; Land</t>
+          <t>Crop Sown Registry - 2. Cultivation and Land Preparation</t>
         </is>
       </c>
       <c r="B2" s="39" t="inlineStr">

--- a/odk/source/crop_sown_registry_prep.xlsx
+++ b/odk/source/crop_sown_registry_prep.xlsx
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G26" s="46" t="inlineStr">
         <is>
-          <t>Actual Cultivated Date (GC) must be between Start Date and End Date.</t>
+          <t>Actual Cultivated Date must be between Start Date and End Date.</t>
         </is>
       </c>
       <c r="H26" s="46" t="n"/>
